--- a/INVENTARIOS IESS ZAMORA.xlsx
+++ b/INVENTARIOS IESS ZAMORA.xlsx
@@ -2704,10 +2704,8 @@
         </is>
       </c>
       <c r="B12" s="43" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="43" t="n">
+        <v>2</v>
       </c>
       <c r="D12" s="146" t="n"/>
       <c r="E12" s="133" t="n"/>
@@ -3875,10 +3873,8 @@
         </is>
       </c>
       <c r="B12" s="43" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="43" t="n">
+        <v>1</v>
       </c>
       <c r="D12" s="146" t="n"/>
       <c r="E12" s="133" t="n"/>
